--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/Omni-SR/OmniSR+50T+50EP+optim_purn/params_vs_psnr_analysis/OmniSR_hutcn_hyperopt_study_3cols.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/Omni-SR/OmniSR+50T+50EP+optim_purn/params_vs_psnr_analysis/OmniSR_hutcn_hyperopt_study_3cols.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FLOPs (G) @ 48x48</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>PSNR (dB)</t>
         </is>
       </c>
@@ -453,6 +458,9 @@
         <v>483382</v>
       </c>
       <c r="C2" t="n">
+        <v>0.999764172</v>
+      </c>
+      <c r="D2" t="n">
         <v>29.00486679077148</v>
       </c>
     </row>
@@ -464,6 +472,9 @@
         <v>1163100</v>
       </c>
       <c r="C3" t="n">
+        <v>2.7360099</v>
+      </c>
+      <c r="D3" t="n">
         <v>28.11308135986328</v>
       </c>
     </row>
@@ -475,6 +486,9 @@
         <v>1451240</v>
       </c>
       <c r="C4" t="n">
+        <v>3.304958976</v>
+      </c>
+      <c r="D4" t="n">
         <v>30.60256423950195</v>
       </c>
     </row>
@@ -486,6 +500,9 @@
         <v>1114064</v>
       </c>
       <c r="C5" t="n">
+        <v>2.419237296</v>
+      </c>
+      <c r="D5" t="n">
         <v>27.89981384277344</v>
       </c>
     </row>
@@ -497,6 +514,9 @@
         <v>272040</v>
       </c>
       <c r="C6" t="n">
+        <v>0.5591232</v>
+      </c>
+      <c r="D6" t="n">
         <v>27.10241432189941</v>
       </c>
     </row>
@@ -508,6 +528,9 @@
         <v>561556</v>
       </c>
       <c r="C7" t="n">
+        <v>1.313421516</v>
+      </c>
+      <c r="D7" t="n">
         <v>27.84151496887207</v>
       </c>
     </row>
@@ -519,6 +542,9 @@
         <v>1000808</v>
       </c>
       <c r="C8" t="n">
+        <v>2.014129152</v>
+      </c>
+      <c r="D8" t="n">
         <v>29.17798461914062</v>
       </c>
     </row>
@@ -530,6 +556,9 @@
         <v>385852</v>
       </c>
       <c r="C9" t="n">
+        <v>0.850428396</v>
+      </c>
+      <c r="D9" t="n">
         <v>24.90312538146973</v>
       </c>
     </row>
@@ -541,6 +570,9 @@
         <v>668748</v>
       </c>
       <c r="C10" t="n">
+        <v>1.36351566</v>
+      </c>
+      <c r="D10" t="n">
         <v>28.00323028564453</v>
       </c>
     </row>
@@ -552,6 +584,9 @@
         <v>584208</v>
       </c>
       <c r="C11" t="n">
+        <v>1.4067756</v>
+      </c>
+      <c r="D11" t="n">
         <v>30.38225173950195</v>
       </c>
     </row>
@@ -563,6 +598,9 @@
         <v>1295332</v>
       </c>
       <c r="C12" t="n">
+        <v>2.733124608</v>
+      </c>
+      <c r="D12" t="n">
         <v>30.51455879211426</v>
       </c>
     </row>
@@ -574,6 +612,9 @@
         <v>1295332</v>
       </c>
       <c r="C13" t="n">
+        <v>2.733124608</v>
+      </c>
+      <c r="D13" t="n">
         <v>30.49529228210449</v>
       </c>
     </row>
@@ -585,6 +626,9 @@
         <v>1115864</v>
       </c>
       <c r="C14" t="n">
+        <v>2.419237296</v>
+      </c>
+      <c r="D14" t="n">
         <v>30.45342979431152</v>
       </c>
     </row>
@@ -596,6 +640,9 @@
         <v>1295332</v>
       </c>
       <c r="C15" t="n">
+        <v>2.733124608</v>
+      </c>
+      <c r="D15" t="n">
         <v>30.54413642883301</v>
       </c>
     </row>
@@ -607,6 +654,9 @@
         <v>1151568</v>
       </c>
       <c r="C16" t="n">
+        <v>2.7360099</v>
+      </c>
+      <c r="D16" t="n">
         <v>30.69737014770508</v>
       </c>
     </row>
@@ -618,6 +668,9 @@
         <v>889456</v>
       </c>
       <c r="C17" t="n">
+        <v>2.02132728</v>
+      </c>
+      <c r="D17" t="n">
         <v>30.71955413818359</v>
       </c>
     </row>
@@ -629,6 +682,9 @@
         <v>889456</v>
       </c>
       <c r="C18" t="n">
+        <v>2.02132728</v>
+      </c>
+      <c r="D18" t="n">
         <v>30.60545120239258</v>
       </c>
     </row>
@@ -640,6 +696,9 @@
         <v>771732</v>
       </c>
       <c r="C19" t="n">
+        <v>1.768706316</v>
+      </c>
+      <c r="D19" t="n">
         <v>30.61178092956543</v>
       </c>
     </row>
@@ -651,6 +710,9 @@
         <v>771732</v>
       </c>
       <c r="C20" t="n">
+        <v>1.768706316</v>
+      </c>
+      <c r="D20" t="n">
         <v>30.57768096923828</v>
       </c>
     </row>
@@ -662,6 +724,9 @@
         <v>1015604</v>
       </c>
       <c r="C21" t="n">
+        <v>2.29060062</v>
+      </c>
+      <c r="D21" t="n">
         <v>30.72742881774902</v>
       </c>
     </row>
@@ -673,6 +738,9 @@
         <v>1151568</v>
       </c>
       <c r="C22" t="n">
+        <v>2.7360099</v>
+      </c>
+      <c r="D22" t="n">
         <v>30.66411781311035</v>
       </c>
     </row>
@@ -684,6 +752,9 @@
         <v>1023292</v>
       </c>
       <c r="C23" t="n">
+        <v>2.29060062</v>
+      </c>
+      <c r="D23" t="n">
         <v>30.57785339355469</v>
       </c>
     </row>
@@ -695,6 +766,9 @@
         <v>1151568</v>
       </c>
       <c r="C24" t="n">
+        <v>2.7360099</v>
+      </c>
+      <c r="D24" t="n">
         <v>30.60219688415527</v>
       </c>
     </row>
@@ -706,6 +780,9 @@
         <v>1008548</v>
       </c>
       <c r="C25" t="n">
+        <v>2.418463152</v>
+      </c>
+      <c r="D25" t="n">
         <v>30.57052917480469</v>
       </c>
     </row>
@@ -717,6 +794,9 @@
         <v>561556</v>
       </c>
       <c r="C26" t="n">
+        <v>1.313421516</v>
+      </c>
+      <c r="D26" t="n">
         <v>30.56224212646485</v>
       </c>
     </row>
@@ -728,6 +808,9 @@
         <v>1304164</v>
       </c>
       <c r="C27" t="n">
+        <v>3.072863232</v>
+      </c>
+      <c r="D27" t="n">
         <v>30.77863502502441</v>
       </c>
     </row>
